--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="虚拟仓库库存" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>SKU</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>实体仓未分配数</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
   </si>
   <si>
     <t>{.usableQty}</t>
@@ -1151,16 +1154,16 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>

--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventory.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventory.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="虚拟仓库库存" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>SKU</t>
   </si>
@@ -75,6 +75,12 @@
     <t>实体仓名称</t>
   </si>
   <si>
+    <t>实体仓实际库存</t>
+  </si>
+  <si>
+    <t>实体仓冻结库存</t>
+  </si>
+  <si>
     <t>实体仓可用库存</t>
   </si>
   <si>
@@ -85,6 +91,12 @@
   </si>
   <si>
     <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.realQty}</t>
+  </si>
+  <si>
+    <t>{.frozenQty}</t>
   </si>
   <si>
     <t>{.usableQty}</t>
@@ -709,8 +721,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1091,21 +1106,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16.375" customWidth="1"/>
-    <col min="4" max="4" width="13.125" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="7" width="14.875" customWidth="1"/>
-    <col min="8" max="8" width="13.75" customWidth="1"/>
-    <col min="9" max="9" width="11.75" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="4" max="4" width="16.125" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="14.875" customWidth="1"/>
+    <col min="9" max="9" width="16.625" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="16.5" customWidth="1"/>
+    <col min="13" max="13" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1121,26 +1139,32 @@
       <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H1" t="s">
         <v>17</v>
       </c>
       <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1154,24 +1178,30 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>12</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>13</v>
       </c>
     </row>
